--- a/docs/design/ACSMS-SCR-031/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_お知らせ一覧画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-031/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_お知らせ一覧画面_V1.0.xlsx
@@ -1356,7 +1356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK82"/>
+  <dimension ref="A1:AK81"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1517,7 +1517,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1871,7 +1871,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2632,7 +2632,7 @@
       <c r="C44" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "OSHIRASE_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定されたお知らせが見つかりません"
 }</t>
         </is>
@@ -2683,7 +2683,7 @@
       <c r="C47" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "HAS_RELATED_DATA",
+  "error_code": "CONFLICT",
   "message": "関連データが存在するため削除できません"
 }</t>
         </is>
@@ -2782,59 +2782,96 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="27" t="inlineStr">
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="D56" s="41" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="D57" s="41" t="inlineStr">
         <is>
           <t>oshirase_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：HTTP 400 (`BAD_REQUEST`)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="C60" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`oshirase.delete` を保持しているか確認する。</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
@@ -2853,21 +2890,14 @@
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
+      <c r="C64" s="41" t="inlineStr">
         <is>
           <t>対象レコードの存在確認。</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="108" customHeight="1">
-      <c r="C66" s="42" t="inlineStr">
+    <row r="65" ht="108" customHeight="1">
+      <c r="C65" s="42" t="inlineStr">
         <is>
           <t>SELECT oshirase_id, ja_id, oshirase_type, publish_location, status,
        title, content, publish_start_date, publish_end_date,
@@ -2877,71 +2907,71 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="n"/>
-      <c r="O66" s="10" t="n"/>
-      <c r="P66" s="10" t="n"/>
-      <c r="Q66" s="10" t="n"/>
-      <c r="R66" s="10" t="n"/>
-      <c r="S66" s="10" t="n"/>
-      <c r="T66" s="10" t="n"/>
-      <c r="U66" s="10" t="n"/>
-      <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
-      <c r="X66" s="10" t="n"/>
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-      <c r="AA66" s="10" t="n"/>
-      <c r="AB66" s="10" t="n"/>
-      <c r="AC66" s="10" t="n"/>
-      <c r="AD66" s="10" t="n"/>
-      <c r="AE66" s="10" t="n"/>
-      <c r="AF66" s="10" t="n"/>
-      <c r="AG66" s="10" t="n"/>
-      <c r="AH66" s="10" t="n"/>
-      <c r="AI66" s="10" t="n"/>
-      <c r="AJ66" s="10" t="n"/>
-      <c r="AK66" s="11" t="n"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`OSHIRASE_NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="36" customHeight="1">
-      <c r="C68" s="41" t="inlineStr">
-        <is>
           <t>関連データの存在確認（将来の拡張に備えた整合性チェック）：関連テーブルにお知らせIDが紐づくレコードが存在する場合、削除を拒否する。現行DBスキーマでは参照テーブルなし。</t>
         </is>
       </c>
     </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
+        </is>
+      </c>
+    </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>関連データが存在する場合：HTTP 409 (`HAS_RELATED_DATA`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+      <c r="B69" s="27" t="inlineStr">
         <is>
           <t>4.4 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="108" customHeight="1">
-      <c r="C71" s="42" t="inlineStr">
+    <row r="70" ht="108" customHeight="1">
+      <c r="C70" s="42" t="inlineStr">
         <is>
           <t>UPDATE t_oshirase
 SET deleted_at = NOW(),
@@ -2951,57 +2981,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>削除前データ（4.3 のSELECT結果）を `before_value` に格納する。</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="216" customHeight="1">
-      <c r="C74" s="42" t="inlineStr">
+    <row r="73" ht="216" customHeight="1">
+      <c r="C73" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -3015,6 +3045,59 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="252" customHeight="1">
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "oshirase_id": 1,
+  "ja_id": null,
+  "oshirase_type": 1,
+  "publish_location": 2,
+  "status": 2,
+  "title": "システムメンテナンスのお知らせ",
+  "publish_start_date": "2026-04-20T09:00:00Z",
+  "publish_end_date": "2026-04-30T23:59:00Z",
+  "target_kanri_kubun": "1,2,3"
+}</t>
         </is>
       </c>
       <c r="D74" s="10" t="n"/>
@@ -3052,137 +3135,84 @@
       <c r="AJ74" s="10" t="n"/>
       <c r="AK74" s="11" t="n"/>
     </row>
-    <row r="75" ht="252" customHeight="1">
-      <c r="C75" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "oshirase_id": 1,
-  "ja_id": null,
-  "oshirase_type": 1,
-  "publish_location": 2,
-  "status": 2,
-  "title": "システムメンテナンスのお知らせ",
-  "publish_start_date": "2026-04-20T09:00:00Z",
-  "publish_end_date": "2026-04-30T23:59:00Z",
-  "target_kanri_kubun": "1,2,3"
-}</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="n"/>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="10" t="n"/>
-      <c r="H75" s="10" t="n"/>
-      <c r="I75" s="10" t="n"/>
-      <c r="J75" s="10" t="n"/>
-      <c r="K75" s="10" t="n"/>
-      <c r="L75" s="10" t="n"/>
-      <c r="M75" s="10" t="n"/>
-      <c r="N75" s="10" t="n"/>
-      <c r="O75" s="10" t="n"/>
-      <c r="P75" s="10" t="n"/>
-      <c r="Q75" s="10" t="n"/>
-      <c r="R75" s="10" t="n"/>
-      <c r="S75" s="10" t="n"/>
-      <c r="T75" s="10" t="n"/>
-      <c r="U75" s="10" t="n"/>
-      <c r="V75" s="10" t="n"/>
-      <c r="W75" s="10" t="n"/>
-      <c r="X75" s="10" t="n"/>
-      <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="10" t="n"/>
-      <c r="AA75" s="10" t="n"/>
-      <c r="AB75" s="10" t="n"/>
-      <c r="AC75" s="10" t="n"/>
-      <c r="AD75" s="10" t="n"/>
-      <c r="AE75" s="10" t="n"/>
-      <c r="AF75" s="10" t="n"/>
-      <c r="AG75" s="10" t="n"/>
-      <c r="AH75" s="10" t="n"/>
-      <c r="AI75" s="10" t="n"/>
-      <c r="AJ75" s="10" t="n"/>
-      <c r="AK75" s="11" t="n"/>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="B76" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>削除完了メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>削除完了メッセージを返却する。HTTP 200。</t>
-        </is>
-      </c>
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>{ "message": "正常に削除しました" }</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
+      <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
-        <is>
-          <t>{ "message": "正常に削除しました" }</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="C80" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="216" customHeight="1">
-      <c r="C82" s="42" t="inlineStr">
+    <row r="81" ht="216" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -3198,47 +3228,46 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="113">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="C66:AK66"/>
@@ -3249,10 +3278,10 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="A53:AK53"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
@@ -3264,11 +3293,11 @@
     <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
@@ -3278,37 +3307,36 @@
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="B69:AK69"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C55:AK55"/>
-    <mergeCell ref="B64:AK64"/>
+    <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
     <mergeCell ref="Y28:AE28"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="B71:AK71"/>
     <mergeCell ref="C32:AK32"/>
     <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C63:AK63"/>
@@ -3316,38 +3344,39 @@
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="B54:AK54"/>
-    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="D68:AK68"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
-    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="B76:AK76"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="B75:AK75"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3521,7 +3550,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3875,7 +3904,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -5032,7 +5061,7 @@
     <row r="58" ht="18" customHeight="1">
       <c r="C58" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5705,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6102,7 +6131,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6548,7 +6577,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="19" t="inlineStr">
         <is>
-          <t>OSHIRASE_NOT_FOUND</t>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="K12" s="10" t="n"/>
@@ -6601,7 +6630,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>HAS_RELATED_DATA</t>
+          <t>CONFLICT</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6654,7 +6683,7 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>締め切り時間_DUPLICATE</t>
+          <t>DEADLINE_NOTICE_DUPLICATE</t>
         </is>
       </c>
       <c r="K14" s="10" t="n"/>
@@ -6917,7 +6946,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7604,7 +7633,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7958,7 +7987,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -10070,7 +10099,7 @@
     <row r="76" ht="18" customHeight="1">
       <c r="C76" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10715,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11040,7 +11069,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -12691,7 +12720,7 @@
       <c r="C58" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "OSHIRASE_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定されたお知らせが見つかりません"
 }</t>
         </is>
@@ -12828,7 +12857,7 @@
     <row r="70" ht="18" customHeight="1">
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -12916,7 +12945,7 @@
     <row r="77" ht="18" customHeight="1">
       <c r="C77" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`OSHIRASE_NOT_FOUND`)</t>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK110"/>
+  <dimension ref="A1:AK109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -13343,7 +13372,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -13697,7 +13726,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -13856,7 +13885,7 @@
       <c r="B17" s="35" t="n"/>
       <c r="I17" s="36" t="n"/>
       <c r="J17" s="17" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
@@ -15884,7 +15913,7 @@
     <row r="66" ht="19.5" customHeight="1">
       <c r="B66" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 409 Conflict（締め切り時間重複））</t>
+          <t>レスポンス（失敗 400 Bad Request（締め切り時間重複））</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15921,7 @@
       <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "締め切り時間_DUPLICATE",
+  "error_code": "DEADLINE_NOTICE_DUPLICATE",
   "message": "公開場所「メニュー画面」かつ種別「締め切り時間」のお知らせが既に存在するため登録できません"
 }</t>
         </is>
@@ -16046,73 +16075,110 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
+    <row r="77" ht="54" customHeight="1">
+      <c r="B77" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="10" t="n"/>
+      <c r="M77" s="10" t="n"/>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="10" t="n"/>
+      <c r="Q77" s="10" t="n"/>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="10" t="n"/>
+      <c r="T77" s="10" t="n"/>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="10" t="n"/>
+      <c r="Y77" s="10" t="n"/>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="10" t="n"/>
+      <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>title：必須、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>publish_location：必須、1 または 2</t>
+          <t>title：必須、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
+          <t>publish_location：必須、1 または 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
+        <is>
           <t>status：必須、1、2 または 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="36" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>publish_start_date：必須、有効な日時形式（YYYY/MM/DD HH:mm）、過去日不可</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
+          <t>publish_start_date：必須、有効な日時形式（YYYY/MM/DD HH:mm）、過去日不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
+        <is>
           <t>publish_end_date：任意、有効な日時形式（YYYY/MM/DD HH:mm）、publish_start_date 以降</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>ja_id：任意、数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>oshirase_type：必須、1、2、3 または 4</t>
+          <t>ja_id：任意、数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>target_kanri_kubun：任意、最大20文字</t>
+          <t>oshirase_type：必須、1、2、3 または 4</t>
         </is>
       </c>
     </row>
@@ -16131,63 +16197,56 @@
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
       <c r="C91" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>権限チェック：`oshirase.create` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`oshirase.create` を保持しているか確認する。</t>
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>4.3 重複チェック（締め切り時間）</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
         <is>
           <t>publish_location = 2（メニュー画面）かつ oshirase_type = 4（締め切り時間）の場合、既存レコードの存在を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="90" customHeight="1">
-      <c r="C97" s="42" t="inlineStr">
+    <row r="96" ht="90" customHeight="1">
+      <c r="C96" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*)
 FROM t_oshirase
@@ -16196,64 +16255,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>既存レコードが存在する場合：HTTP 400 (`DEADLINE_NOTICE_DUPLICATE`)</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>既存レコードが存在する場合：HTTP 409 (`締め切り時間_DUPLICATE`)</t>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ登録</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ登録</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
         <is>
           <t>target_kanri_kubun が未入力の場合、空文字列を設定する（全区分対象）。</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="162" customHeight="1">
-      <c r="C101" s="42" t="inlineStr">
+    <row r="100" ht="162" customHeight="1">
+      <c r="C100" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_oshirase (ja_id, oshirase_type, publish_location, status,
                         title, content, publish_start_date, publish_end_date,
@@ -16266,50 +16325,50 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D101" s="10" t="n"/>
-      <c r="E101" s="10" t="n"/>
-      <c r="F101" s="10" t="n"/>
-      <c r="G101" s="10" t="n"/>
-      <c r="H101" s="10" t="n"/>
-      <c r="I101" s="10" t="n"/>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="10" t="n"/>
-      <c r="M101" s="10" t="n"/>
-      <c r="N101" s="10" t="n"/>
-      <c r="O101" s="10" t="n"/>
-      <c r="P101" s="10" t="n"/>
-      <c r="Q101" s="10" t="n"/>
-      <c r="R101" s="10" t="n"/>
-      <c r="S101" s="10" t="n"/>
-      <c r="T101" s="10" t="n"/>
-      <c r="U101" s="10" t="n"/>
-      <c r="V101" s="10" t="n"/>
-      <c r="W101" s="10" t="n"/>
-      <c r="X101" s="10" t="n"/>
-      <c r="Y101" s="10" t="n"/>
-      <c r="Z101" s="10" t="n"/>
-      <c r="AA101" s="10" t="n"/>
-      <c r="AB101" s="10" t="n"/>
-      <c r="AC101" s="10" t="n"/>
-      <c r="AD101" s="10" t="n"/>
-      <c r="AE101" s="10" t="n"/>
-      <c r="AF101" s="10" t="n"/>
-      <c r="AG101" s="10" t="n"/>
-      <c r="AH101" s="10" t="n"/>
-      <c r="AI101" s="10" t="n"/>
-      <c r="AJ101" s="10" t="n"/>
-      <c r="AK101" s="11" t="n"/>
-    </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="216" customHeight="1">
-      <c r="C103" s="42" t="inlineStr">
+    <row r="102" ht="216" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -16323,6 +16382,59 @@
         '', :after_value_json,
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="252" customHeight="1">
+      <c r="C103" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：INSERT のため空文字列を設定する。
+`after_value`：登録されたデータをJSON形式で格納する。
+{
+  "oshirase_id": 10,
+  "ja_id": null,
+  "oshirase_type": 1,
+  "publish_location": 2,
+  "status": 2,
+  "title": "システムメンテナンスのお知らせ",
+  "publish_start_date": "2026-04-20T09:00:00Z",
+  "publish_end_date": "2026-04-30T23:59:00Z",
+  "target_kanri_kubun": "1,2,3"
+}</t>
         </is>
       </c>
       <c r="D103" s="10" t="n"/>
@@ -16360,96 +16472,43 @@
       <c r="AJ103" s="10" t="n"/>
       <c r="AK103" s="11" t="n"/>
     </row>
-    <row r="104" ht="252" customHeight="1">
-      <c r="C104" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：INSERT のため空文字列を設定する。
-`after_value`：登録されたデータをJSON形式で格納する。
-{
-  "oshirase_id": 10,
-  "ja_id": null,
-  "oshirase_type": 1,
-  "publish_location": 2,
-  "status": 2,
-  "title": "システムメンテナンスのお知らせ",
-  "publish_start_date": "2026-04-20T09:00:00Z",
-  "publish_end_date": "2026-04-30T23:59:00Z",
-  "target_kanri_kubun": "1,2,3"
-}</t>
-        </is>
-      </c>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="10" t="n"/>
-      <c r="F104" s="10" t="n"/>
-      <c r="G104" s="10" t="n"/>
-      <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="10" t="n"/>
-      <c r="K104" s="10" t="n"/>
-      <c r="L104" s="10" t="n"/>
-      <c r="M104" s="10" t="n"/>
-      <c r="N104" s="10" t="n"/>
-      <c r="O104" s="10" t="n"/>
-      <c r="P104" s="10" t="n"/>
-      <c r="Q104" s="10" t="n"/>
-      <c r="R104" s="10" t="n"/>
-      <c r="S104" s="10" t="n"/>
-      <c r="T104" s="10" t="n"/>
-      <c r="U104" s="10" t="n"/>
-      <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
-      <c r="X104" s="10" t="n"/>
-      <c r="Y104" s="10" t="n"/>
-      <c r="Z104" s="10" t="n"/>
-      <c r="AA104" s="10" t="n"/>
-      <c r="AB104" s="10" t="n"/>
-      <c r="AC104" s="10" t="n"/>
-      <c r="AD104" s="10" t="n"/>
-      <c r="AE104" s="10" t="n"/>
-      <c r="AF104" s="10" t="n"/>
-      <c r="AG104" s="10" t="n"/>
-      <c r="AH104" s="10" t="n"/>
-      <c r="AI104" s="10" t="n"/>
-      <c r="AJ104" s="10" t="n"/>
-      <c r="AK104" s="11" t="n"/>
+    <row r="104" ht="18" customHeight="1">
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1">
-      <c r="B105" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
+      <c r="C105" s="41" t="inlineStr">
+        <is>
+          <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>登録されたデータを data オブジェクトとして返却する。HTTP 201。</t>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="B107" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
+      <c r="C107" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="C108" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="216" customHeight="1">
-      <c r="C110" s="42" t="inlineStr">
+    <row r="109" ht="216" customHeight="1">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -16465,44 +16524,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
-      <c r="P110" s="10" t="n"/>
-      <c r="Q110" s="10" t="n"/>
-      <c r="R110" s="10" t="n"/>
-      <c r="S110" s="10" t="n"/>
-      <c r="T110" s="10" t="n"/>
-      <c r="U110" s="10" t="n"/>
-      <c r="V110" s="10" t="n"/>
-      <c r="W110" s="10" t="n"/>
-      <c r="X110" s="10" t="n"/>
-      <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="10" t="n"/>
-      <c r="AA110" s="10" t="n"/>
-      <c r="AB110" s="10" t="n"/>
-      <c r="AC110" s="10" t="n"/>
-      <c r="AD110" s="10" t="n"/>
-      <c r="AE110" s="10" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
-      <c r="AI110" s="10" t="n"/>
-      <c r="AJ110" s="10" t="n"/>
-      <c r="AK110" s="11" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="10" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="10" t="n"/>
+      <c r="O109" s="10" t="n"/>
+      <c r="P109" s="10" t="n"/>
+      <c r="Q109" s="10" t="n"/>
+      <c r="R109" s="10" t="n"/>
+      <c r="S109" s="10" t="n"/>
+      <c r="T109" s="10" t="n"/>
+      <c r="U109" s="10" t="n"/>
+      <c r="V109" s="10" t="n"/>
+      <c r="W109" s="10" t="n"/>
+      <c r="X109" s="10" t="n"/>
+      <c r="Y109" s="10" t="n"/>
+      <c r="Z109" s="10" t="n"/>
+      <c r="AA109" s="10" t="n"/>
+      <c r="AB109" s="10" t="n"/>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="10" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="266">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="265">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
@@ -16516,6 +16574,7 @@
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="B72:I72"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="A76:AK76"/>
     <mergeCell ref="Q31:S31"/>
@@ -16545,7 +16604,6 @@
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="A34:AK34"/>
     <mergeCell ref="C91:AK91"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
@@ -16559,6 +16617,7 @@
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
@@ -16566,7 +16625,6 @@
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
@@ -16578,18 +16636,18 @@
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="C88:AK88"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -16597,13 +16655,13 @@
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="C103:AK103"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
@@ -16611,17 +16669,17 @@
     <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="M51:P51"/>
-    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="B89:AK89"/>
+    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
     <mergeCell ref="T46:X46"/>
@@ -16641,7 +16699,6 @@
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="T45:X45"/>
@@ -16654,8 +16711,9 @@
     <mergeCell ref="C37:L37"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="D92:AK92"/>
     <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -16667,6 +16725,7 @@
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
@@ -16680,6 +16739,7 @@
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="D80:AK80"/>
@@ -16687,11 +16747,14 @@
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="AC32:AE32"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
@@ -16711,7 +16774,6 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B105:AK105"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="B14:I19"/>
@@ -16720,11 +16782,9 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="B98:AK98"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="B107:AK107"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
@@ -16736,7 +16796,6 @@
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="D85:AK85"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
@@ -16760,7 +16819,6 @@
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="C38:C52"/>
-    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="D45:L45"/>
@@ -16940,7 +16998,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -17294,7 +17352,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -19549,7 +19607,7 @@
       <c r="C68" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "OSHIRASE_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定されたお知らせが見つかりません"
 }</t>
         </is>
@@ -19702,73 +19760,110 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+    <row r="78" ht="54" customHeight="1">
+      <c r="B78" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータ：oshirase_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="C80" s="41" t="inlineStr">
         <is>
+          <t>パスパラメータ：oshirase_id 数値型チェック、必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
+        <is>
           <t>リクエストボディの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>title：必須、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>publish_location：必須、1 または 2</t>
+          <t>title：必須、最大200文字</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
+          <t>publish_location：必須、1 または 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
+        <is>
           <t>status：必須、1、2 または 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>publish_start_date：必須、有効な日時形式（YYYY/MM/DD HH:mm）。過去日の場合は変更不可（サーバー側でも確認）</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
+          <t>publish_start_date：必須、有効な日時形式（YYYY/MM/DD HH:mm）。過去日の場合は変更不可（サーバー側でも確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
           <t>publish_end_date：任意、有効な日時形式（YYYY/MM/DD HH:mm）、publish_start_date 以降。過去日または未設定の場合のみ変更可能</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>ja_id：任意、数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>oshirase_type：必須、1、2、3 または 4</t>
+          <t>ja_id：任意、数値型チェック</t>
         </is>
       </c>
     </row>
@@ -19803,7 +19898,7 @@
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -19891,7 +19986,7 @@
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`OSHIRASE_NOT_FOUND`)</t>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20431,6 @@
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="J13:AK13"/>
@@ -20346,6 +20440,7 @@
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="B64:I64"/>
     <mergeCell ref="Y26:AB26"/>
@@ -20363,6 +20458,7 @@
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="AF25:AK25"/>
@@ -20395,7 +20491,6 @@
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="B67:I67"/>
     <mergeCell ref="J8:AK8"/>
